--- a/data/trans_dic/IP19C01-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C01-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por revisión o chequeo</t>
+          <t>Menores que en su última visita al dentista fue por revisión o chequeo (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,87; 75,14</t>
+          <t>53,09; 75,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63,45; 83,14</t>
+          <t>62,53; 82,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,71; 79,31</t>
+          <t>45,44; 78,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47,63; 91,0</t>
+          <t>49,47; 91,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>58,69; 80,64</t>
+          <t>58,45; 80,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,96; 83,61</t>
+          <t>61,54; 84,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,93; 83,02</t>
+          <t>55,5; 83,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>68,29; 95,11</t>
+          <t>69,28; 94,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>59,11; 74,65</t>
+          <t>59,26; 75,34</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65,69; 80,68</t>
+          <t>65,86; 81,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54,93; 76,48</t>
+          <t>55,88; 76,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64,62; 89,87</t>
+          <t>63,97; 90,29</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>57,73; 67,95</t>
+          <t>58,19; 68,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>64,57; 74,49</t>
+          <t>63,75; 74,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,58; 77,28</t>
+          <t>68,41; 77,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,82; 87,7</t>
+          <t>79,83; 87,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,97; 75,48</t>
+          <t>66,2; 75,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,24; 78,23</t>
+          <t>68,94; 77,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,77; 82,25</t>
+          <t>74,24; 82,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>74,75; 84,03</t>
+          <t>74,32; 84,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63,7; 70,53</t>
+          <t>63,7; 70,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67,52; 74,83</t>
+          <t>68,04; 75,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72,37; 78,52</t>
+          <t>72,41; 78,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,66; 85,01</t>
+          <t>78,48; 84,85</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67,5; 83,27</t>
+          <t>67,82; 84,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69,88; 84,91</t>
+          <t>70,52; 85,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71,19; 85,33</t>
+          <t>71,78; 85,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68,85; 83,95</t>
+          <t>69,28; 83,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63,63; 80,68</t>
+          <t>63,62; 81,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,49; 90,09</t>
+          <t>76,8; 89,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63,03; 78,74</t>
+          <t>62,3; 79,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80,93; 92,18</t>
+          <t>81,16; 91,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68,73; 80,54</t>
+          <t>69,17; 80,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75,69; 85,81</t>
+          <t>75,72; 85,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68,88; 79,35</t>
+          <t>68,99; 79,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>78,05; 86,95</t>
+          <t>78,14; 87,05</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,4; 69,76</t>
+          <t>61,94; 69,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67,86; 75,75</t>
+          <t>68,27; 75,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69,6; 77,51</t>
+          <t>69,4; 77,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77,96; 84,91</t>
+          <t>78,06; 85,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,59; 75,19</t>
+          <t>67,68; 75,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,97; 79,4</t>
+          <t>72,12; 79,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,19; 79,68</t>
+          <t>72,03; 79,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78,51; 85,69</t>
+          <t>78,33; 85,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>65,89; 71,63</t>
+          <t>65,98; 71,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71,46; 76,69</t>
+          <t>71,36; 76,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72,09; 77,36</t>
+          <t>71,97; 77,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,73; 84,54</t>
+          <t>79,27; 84,32</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por revisión o chequeo (tasa de respuesta: 99,77%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>30345</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>35372</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14589</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22645</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>30256</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>31866</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>19964</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>21672</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>60600</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>67239</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>34554</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>44317</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>24913; 35286</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29992; 39746</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10470; 18146</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14708; 27219</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>25070; 34492</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>26437; 36192</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>15946; 23934</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>17656; 24059</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>53229; 67670</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>59887; 73765</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>28932; 39734</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>35323; 49851</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>144179</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>154504</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>184292</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>220107</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>174257</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>178006</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>199704</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>258685</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>318436</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>332510</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>383996</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>478791</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>132850; 155983</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>141858; 164937</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>173397; 195348</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>209014; 230059</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>162664; 185344</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>167051; 188795</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>189279; 210853</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>240049; 272746</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>301964; 335510</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>316269; 348880</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>368159; 399032</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>458963; 496239</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>57694</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>66916</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>69686</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>77115</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>53707</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>69259</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>62306</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>118915</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>111401</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>136176</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>131991</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>196029</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>51330; 63648</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>60329; 73204</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>63539; 75993</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69338; 83978</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>46515; 59318</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>63072; 73687</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>54639; 69351</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>110327; 124945</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>102920; 119525</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>126969; 143329</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>121573; 140800</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>184429; 205449</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>232218</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>256792</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>268568</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>319866</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>258220</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>279132</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>281974</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>399272</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>490437</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>535924</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>550541</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>719137</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>217367; 245325</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>243057; 269024</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>253328; 282120</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>305727; 332886</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>244823; 271292</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>264985; 292453</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>267518; 294469</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>379470; 414420</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>470225; 511548</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>516222; 555101</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>529969; 569772</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>694445; 738683</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C01-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C01-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,09; 75,19</t>
+          <t>53,65; 76,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62,53; 82,87</t>
+          <t>61,3; 82,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,44; 78,75</t>
+          <t>42,5; 76,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,47; 91,55</t>
+          <t>48,91; 90,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>58,45; 80,42</t>
+          <t>59,43; 81,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,54; 84,24</t>
+          <t>61,33; 84,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,5; 83,3</t>
+          <t>54,35; 82,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69,28; 94,41</t>
+          <t>66,47; 94,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>59,26; 75,34</t>
+          <t>58,92; 74,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65,86; 81,12</t>
+          <t>65,48; 80,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55,88; 76,74</t>
+          <t>56,58; 76,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,97; 90,29</t>
+          <t>63,02; 90,05</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,19; 68,32</t>
+          <t>57,43; 67,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,75; 74,13</t>
+          <t>64,04; 74,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,41; 77,07</t>
+          <t>67,87; 77,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,83; 87,87</t>
+          <t>79,36; 87,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,2; 75,43</t>
+          <t>66,29; 75,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,94; 77,92</t>
+          <t>68,38; 77,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,24; 82,7</t>
+          <t>73,92; 82,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>74,32; 84,44</t>
+          <t>75,08; 84,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63,7; 70,78</t>
+          <t>63,48; 70,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68,04; 75,06</t>
+          <t>67,85; 74,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72,41; 78,48</t>
+          <t>72,29; 78,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,48; 84,85</t>
+          <t>78,57; 85,05</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67,82; 84,1</t>
+          <t>68,05; 83,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70,52; 85,57</t>
+          <t>70,67; 86,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71,78; 85,85</t>
+          <t>70,96; 85,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69,28; 83,91</t>
+          <t>69,75; 83,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63,62; 81,13</t>
+          <t>63,98; 80,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,8; 89,73</t>
+          <t>76,11; 89,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,3; 79,08</t>
+          <t>63,25; 79,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81,16; 91,91</t>
+          <t>81,62; 92,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>69,17; 80,33</t>
+          <t>68,47; 80,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75,72; 85,48</t>
+          <t>75,67; 85,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68,99; 79,9</t>
+          <t>68,92; 79,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>78,14; 87,05</t>
+          <t>78,52; 87,17</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,94; 69,91</t>
+          <t>61,72; 69,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>68,27; 75,56</t>
+          <t>68,27; 76,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69,4; 77,29</t>
+          <t>69,72; 77,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78,06; 85,0</t>
+          <t>77,71; 84,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,68; 75,0</t>
+          <t>67,62; 74,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,12; 79,6</t>
+          <t>72,1; 79,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,03; 79,29</t>
+          <t>72,19; 79,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78,33; 85,55</t>
+          <t>78,68; 85,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>65,98; 71,78</t>
+          <t>66,07; 71,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71,36; 76,73</t>
+          <t>71,43; 76,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71,97; 77,37</t>
+          <t>72,01; 77,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,27; 84,32</t>
+          <t>79,53; 84,44</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24913; 35286</t>
+          <t>25176; 35666</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29992; 39746</t>
+          <t>29400; 39569</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10470; 18146</t>
+          <t>9794; 17601</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14708; 27219</t>
+          <t>14541; 26950</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25070; 34492</t>
+          <t>25492; 34744</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26437; 36192</t>
+          <t>26348; 36151</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15946; 23934</t>
+          <t>15618; 23744</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17656; 24059</t>
+          <t>16940; 24188</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>53229; 67670</t>
+          <t>52915; 66940</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59887; 73765</t>
+          <t>59543; 73520</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28932; 39734</t>
+          <t>29297; 39617</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35323; 49851</t>
+          <t>34798; 49723</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>132850; 155983</t>
+          <t>131115; 154664</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>141858; 164937</t>
+          <t>142504; 165908</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>173397; 195348</t>
+          <t>172032; 195686</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>209014; 230059</t>
+          <t>207797; 229252</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>162664; 185344</t>
+          <t>162899; 185680</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>167051; 188795</t>
+          <t>165685; 188765</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>189279; 210853</t>
+          <t>188461; 209824</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>240049; 272746</t>
+          <t>242516; 272953</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>301964; 335510</t>
+          <t>300910; 334186</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>316269; 348880</t>
+          <t>315401; 347833</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>368159; 399032</t>
+          <t>367521; 400682</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>458963; 496239</t>
+          <t>459494; 497396</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>51330; 63648</t>
+          <t>51501; 63546</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60329; 73204</t>
+          <t>60454; 73969</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63539; 75993</t>
+          <t>62814; 75438</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69338; 83978</t>
+          <t>69801; 84003</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>46515; 59318</t>
+          <t>46782; 58916</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63072; 73687</t>
+          <t>62509; 73458</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54639; 69351</t>
+          <t>55468; 69661</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>110327; 124945</t>
+          <t>110958; 125384</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>102920; 119525</t>
+          <t>101877; 119386</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>126969; 143329</t>
+          <t>126886; 143521</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>121573; 140800</t>
+          <t>121440; 140745</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>184429; 205449</t>
+          <t>185313; 205741</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>217367; 245325</t>
+          <t>216587; 244928</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>243057; 269024</t>
+          <t>243040; 270963</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>253328; 282120</t>
+          <t>254511; 283010</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>305727; 332886</t>
+          <t>304341; 332207</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>244823; 271292</t>
+          <t>244598; 271064</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>264985; 292453</t>
+          <t>264906; 292529</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>267518; 294469</t>
+          <t>268115; 294193</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>379470; 414420</t>
+          <t>381145; 414784</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>470225; 511548</t>
+          <t>470844; 509320</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>516222; 555101</t>
+          <t>516752; 553917</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>529969; 569772</t>
+          <t>530285; 568634</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>694445; 738683</t>
+          <t>696742; 739765</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C01-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C01-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>70,54%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>74,17%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>69,48%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>84,71%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>64,67%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>73,75%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>63,32%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>76,17%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>70,54%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>74,17%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>69,48%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>83,53%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,65; 76,0</t>
+          <t>58,69; 80,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>61,3; 82,5</t>
+          <t>60,96; 83,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42,5; 76,39</t>
+          <t>54,93; 83,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,91; 90,65</t>
+          <t>67,68; 95,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>59,43; 81,01</t>
+          <t>52,87; 75,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,33; 84,14</t>
+          <t>63,45; 83,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,35; 82,63</t>
+          <t>44,71; 79,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>66,47; 94,92</t>
+          <t>68,26; 92,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58,92; 74,53</t>
+          <t>59,11; 74,65</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65,48; 80,85</t>
+          <t>65,69; 80,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56,58; 76,52</t>
+          <t>54,93; 76,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,02; 90,05</t>
+          <t>73,38; 91,66</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>70,92%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>73,46%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>78,32%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>80,33%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>63,15%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>69,44%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>72,71%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>84,07%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>70,92%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>73,46%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>78,32%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>57,43; 67,74</t>
+          <t>65,97; 75,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>64,04; 74,56</t>
+          <t>68,24; 78,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,87; 77,2</t>
+          <t>73,77; 82,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,36; 87,56</t>
+          <t>75,23; 84,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,29; 75,56</t>
+          <t>57,73; 67,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,38; 77,9</t>
+          <t>64,57; 74,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,92; 82,29</t>
+          <t>67,58; 77,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>75,08; 84,5</t>
+          <t>79,56; 87,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63,48; 70,5</t>
+          <t>63,7; 70,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67,85; 74,83</t>
+          <t>67,52; 74,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72,29; 78,81</t>
+          <t>72,37; 78,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,57; 85,05</t>
+          <t>78,43; 84,98</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>73,45%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>84,33%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>71,05%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>87,56%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>76,23%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>78,22%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>78,72%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>77,06%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>73,45%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>71,05%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68,05; 83,96</t>
+          <t>63,63; 80,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70,67; 86,46</t>
+          <t>76,49; 90,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70,96; 85,22</t>
+          <t>63,03; 78,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69,75; 83,94</t>
+          <t>81,62; 92,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63,98; 80,58</t>
+          <t>67,5; 83,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,11; 89,45</t>
+          <t>69,88; 84,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63,25; 79,43</t>
+          <t>71,19; 85,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81,62; 92,23</t>
+          <t>68,74; 83,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68,47; 80,23</t>
+          <t>68,73; 80,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75,67; 85,6</t>
+          <t>75,69; 85,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68,92; 79,87</t>
+          <t>68,88; 79,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>78,52; 87,17</t>
+          <t>77,96; 86,76</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>71,38%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>75,98%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>75,92%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>82,56%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>66,17%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>72,13%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>73,58%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>81,67%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>71,38%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>75,98%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>75,92%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,72; 69,79</t>
+          <t>67,59; 75,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>68,27; 76,11</t>
+          <t>71,97; 79,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69,72; 77,53</t>
+          <t>72,19; 79,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77,71; 84,83</t>
+          <t>78,56; 85,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,62; 74,94</t>
+          <t>61,4; 69,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,1; 79,62</t>
+          <t>67,86; 75,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,19; 79,21</t>
+          <t>69,6; 77,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78,68; 85,62</t>
+          <t>78,44; 85,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66,07; 71,47</t>
+          <t>65,89; 71,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71,43; 76,57</t>
+          <t>71,46; 76,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72,01; 77,22</t>
+          <t>72,09; 77,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,53; 84,44</t>
+          <t>79,84; 84,58</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1373,37 +1373,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>30256</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>31866</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19964</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20575</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>30345</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>35372</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>14589</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22645</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>30256</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31866</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>19964</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21672</t>
+          <t>21969</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44317</t>
+          <t>42543</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>25176; 35666</t>
+          <t>25172; 34588</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29400; 39569</t>
+          <t>26190; 35923</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9794; 17601</t>
+          <t>15783; 23854</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14541; 26950</t>
+          <t>16440; 23137</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25492; 34744</t>
+          <t>24810; 35261</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26348; 36151</t>
+          <t>30433; 39876</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15618; 23744</t>
+          <t>10303; 18275</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16940; 24188</t>
+          <t>18186; 24628</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52915; 66940</t>
+          <t>53086; 67046</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59543; 73520</t>
+          <t>59731; 73362</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29297; 39617</t>
+          <t>28440; 39599</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34798; 49723</t>
+          <t>37377; 46686</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>218</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>266</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>311</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>174257</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>178006</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>199704</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>248656</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>144179</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>154504</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>184292</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>220107</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>174257</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>178006</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>199704</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>258685</t>
+          <t>222638</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>478791</t>
+          <t>471294</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>131115; 154664</t>
+          <t>162097; 185480</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>142504; 165908</t>
+          <t>165343; 189566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>172032; 195686</t>
+          <t>188103; 209701</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>207797; 229252</t>
+          <t>232862; 260823</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>162899; 185680</t>
+          <t>131816; 155148</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>165685; 188765</t>
+          <t>143668; 165755</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>188461; 209824</t>
+          <t>171300; 195880</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>242516; 272953</t>
+          <t>211681; 232266</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>300910; 334186</t>
+          <t>301948; 334338</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>315401; 347833</t>
+          <t>313860; 347803</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>367521; 400682</t>
+          <t>367957; 399245</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>459494; 497396</t>
+          <t>451431; 489162</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>119</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>53707</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69259</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>62306</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>111427</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>57694</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>66916</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>69686</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>77115</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>53707</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>69259</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>62306</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>118915</t>
+          <t>79803</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>196029</t>
+          <t>191229</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>51501; 63546</t>
+          <t>46525; 58992</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60454; 73969</t>
+          <t>62815; 73983</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62814; 75438</t>
+          <t>55272; 69053</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69801; 84003</t>
+          <t>103865; 117273</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>46782; 58916</t>
+          <t>51083; 63020</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62509; 73458</t>
+          <t>59779; 72635</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55468; 69661</t>
+          <t>63015; 75529</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>110958; 125384</t>
+          <t>71205; 86860</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>101877; 119386</t>
+          <t>102271; 119844</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>126886; 143521</t>
+          <t>126905; 143875</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>121440; 140745</t>
+          <t>121382; 139832</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>185313; 205741</t>
+          <t>179967; 200284</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>363</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>386</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>460</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>473</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>258220</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>279132</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>281974</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>380658</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>232218</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>256792</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>268568</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>319866</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>258220</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>279132</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>281974</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>399272</t>
+          <t>324410</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>719137</t>
+          <t>705067</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>216587; 244928</t>
+          <t>244477; 272001</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>243040; 270963</t>
+          <t>264423; 291726</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>254511; 283010</t>
+          <t>268126; 295931</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>304341; 332207</t>
+          <t>362215; 394644</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>244598; 271064</t>
+          <t>215484; 244818</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>264906; 292529</t>
+          <t>241589; 269703</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>268115; 294193</t>
+          <t>254062; 282940</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>381145; 414784</t>
+          <t>310839; 337298</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>470844; 509320</t>
+          <t>469582; 510472</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>516752; 553917</t>
+          <t>516958; 554768</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>530285; 568634</t>
+          <t>530895; 569710</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>696742; 739765</t>
+          <t>684521; 725196</t>
         </is>
       </c>
     </row>
